--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_58_R6.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_58_R6.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0907</v>
+        <v>-0.0527</v>
       </c>
       <c r="E2" t="n">
-        <v>-1.0582</v>
+        <v>-0.8655</v>
       </c>
       <c r="F2" t="n">
-        <v>1.1489</v>
+        <v>0.8128</v>
       </c>
       <c r="G2" t="n">
         <v>-0.664</v>
@@ -610,13 +610,13 @@
         <v>0.6959</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2908</v>
+        <v>0.1474</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4481</v>
+        <v>-0.2555</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7389</v>
+        <v>0.4028</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>O. DA SILVA</t>
+          <t>S. JOVIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,58 +643,58 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0142</v>
+        <v>-0.0587</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5507</v>
+        <v>0.1189</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.5365</v>
+        <v>-0.1776</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.1113</v>
+        <v>-0.0941</v>
       </c>
       <c r="H3" t="n">
-        <v>1.3647</v>
+        <v>-0.7765</v>
       </c>
       <c r="I3" t="n">
-        <v>-2.476</v>
+        <v>0.6825</v>
       </c>
       <c r="J3" t="n">
-        <v>1.1438</v>
+        <v>1.8328</v>
       </c>
       <c r="K3" t="n">
-        <v>2.0908</v>
+        <v>0.6218</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.947</v>
+        <v>1.211</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.2551</v>
+        <v>-1.9269</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.7261</v>
+        <v>-1.3983</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.529</v>
+        <v>-0.5286</v>
       </c>
       <c r="P3" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q3" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q3" t="n">
-        <v>-2.3195</v>
-      </c>
       <c r="R3" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S3" t="n">
-        <v>2.2852</v>
+        <v>0.2673</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7264</v>
+        <v>-0.5542</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5588</v>
+        <v>0.8215</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>S. JOVIC</t>
+          <t>A. OBST</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,58 +721,58 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.2513</v>
+        <v>-0.5432</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0737</v>
+        <v>2.1899</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1776</v>
+        <v>-2.7332</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0941</v>
+        <v>-0.4951</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.7765</v>
+        <v>-0.2508</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6825</v>
+        <v>-0.2443</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8328</v>
+        <v>4.0728</v>
       </c>
       <c r="K4" t="n">
-        <v>0.6218</v>
+        <v>1.684</v>
       </c>
       <c r="L4" t="n">
-        <v>1.211</v>
+        <v>2.3888</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.9269</v>
+        <v>-4.5679</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3983</v>
+        <v>-1.9348</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.5286</v>
+        <v>-2.6331</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q4" t="n">
         <v>-1.1598</v>
       </c>
       <c r="R4" t="n">
-        <v>0.9278</v>
+        <v>1.6237</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0747</v>
+        <v>-0.512</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7468</v>
+        <v>-0.7231</v>
       </c>
       <c r="U4" t="n">
-        <v>0.8215</v>
+        <v>0.2111</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. OBST</t>
+          <t>N. GIFFEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.325</v>
+        <v>-0.8005</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6435</v>
+        <v>-0.1748</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.9684</v>
+        <v>-0.6257</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4951</v>
+        <v>-2.7868</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.2508</v>
+        <v>-0.468</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2443</v>
+        <v>-2.3188</v>
       </c>
       <c r="J5" t="n">
-        <v>4.0728</v>
+        <v>-0.6889999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>1.684</v>
+        <v>0.1008</v>
       </c>
       <c r="L5" t="n">
-        <v>2.3888</v>
+        <v>-0.7899</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.5679</v>
+        <v>-2.0978</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.9348</v>
+        <v>-0.5688</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.6331</v>
+        <v>-1.529</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>0.9278</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>-0.232</v>
       </c>
       <c r="R5" t="n">
-        <v>1.6237</v>
+        <v>1.1598</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.2937</v>
+        <v>-0.0136</v>
       </c>
       <c r="T5" t="n">
-        <v>-1.2696</v>
+        <v>-0.326</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0242</v>
+        <v>0.3123</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. GIFFEY</t>
+          <t>O. DA SILVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.2893</v>
+        <v>-1.5789</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.193</v>
+        <v>-0.908</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.0962</v>
+        <v>-0.671</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.7868</v>
+        <v>-1.1113</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.468</v>
+        <v>1.3647</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.3188</v>
+        <v>-2.476</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.6889999999999999</v>
+        <v>1.1438</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1008</v>
+        <v>2.0908</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.7899</v>
+        <v>-0.947</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0978</v>
+        <v>-2.2551</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5688</v>
+        <v>-0.7261</v>
       </c>
       <c r="O6" t="n">
         <v>-1.529</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.232</v>
+        <v>-2.3195</v>
       </c>
       <c r="R6" t="n">
         <v>1.1598</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5024</v>
+        <v>0.6921</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.3443</v>
+        <v>0.2677</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1581</v>
+        <v>0.4244</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4347</v>
+        <v>-2.1748</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.5857</v>
+        <v>-1.3931</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.849</v>
+        <v>-0.7817</v>
       </c>
       <c r="G7" t="n">
         <v>-2.0982</v>
@@ -1000,13 +1000,13 @@
         <v>0.232</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.5685</v>
+        <v>-0.3086</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2987</v>
+        <v>-0.1061</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.2697</v>
+        <v>-0.2025</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. GABRIEL</t>
+          <t>J. HOLLATZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.526</v>
+        <v>-2.3602</v>
       </c>
       <c r="E8" t="n">
-        <v>-3.2485</v>
+        <v>-2.0316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7225</v>
+        <v>-0.3286</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.4559</v>
+        <v>-1.9181</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.4994</v>
+        <v>0.1297</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0436</v>
+        <v>-2.0478</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5049</v>
+        <v>-1.2534</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.7625999999999999</v>
+        <v>0.3193</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2576</v>
+        <v>-1.5727</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.9509</v>
+        <v>-0.6647</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.7369</v>
+        <v>-0.1896</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.214</v>
+        <v>-0.4751</v>
       </c>
       <c r="P8" t="n">
-        <v>-2.7834</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q8" t="n">
-        <v>-3.7112</v>
+        <v>-1.1598</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9278</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1.7133</v>
+        <v>0.7176</v>
       </c>
       <c r="T8" t="n">
-        <v>0.8259</v>
+        <v>0.3815</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8874</v>
+        <v>0.3361</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0.1418</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>J. HOLLATZ</t>
+          <t>L. KRATZER</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.6798</v>
+        <v>-2.5046</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1496</v>
+        <v>-1.9242</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.5303</v>
+        <v>-0.5804</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.9181</v>
+        <v>-0.8944</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1297</v>
+        <v>-1.1186</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.0478</v>
+        <v>0.2242</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2534</v>
+        <v>0.8001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.3193</v>
+        <v>0.1008</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.5727</v>
+        <v>0.6993</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6647</v>
+        <v>-1.6945</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.1896</v>
+        <v>-1.2195</v>
       </c>
       <c r="O9" t="n">
         <v>-0.4751</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.1598</v>
+        <v>-1.6237</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.398</v>
+        <v>0.1553</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2636</v>
+        <v>-0.4048</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1344</v>
+        <v>0.5601</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>L. KRATZER</t>
+          <t>X. RATHAN-MAYES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.7644</v>
+        <v>-2.7735</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1168</v>
+        <v>-2.5741</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6476</v>
+        <v>-0.1993</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8944</v>
+        <v>-3.4787</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.1186</v>
+        <v>-2.9231</v>
       </c>
       <c r="I10" t="n">
-        <v>0.2242</v>
+        <v>-0.5556</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8001</v>
+        <v>-2.2775</v>
       </c>
       <c r="K10" t="n">
-        <v>0.1008</v>
+        <v>-2.0397</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6993</v>
+        <v>-0.2378</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.6945</v>
+        <v>-1.2012</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.2195</v>
+        <v>-0.8834</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.4751</v>
+        <v>-0.3178</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6237</v>
+        <v>-0.232</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.3195</v>
+        <v>-1.3917</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>1.1598</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1046</v>
+        <v>0.4011</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5975</v>
+        <v>0.2754</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4929</v>
+        <v>0.1256</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1418</v>
+        <v>0.5361</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.8197</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X. RATHAN-MAYES</t>
+          <t>W. GABRIEL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.1438</v>
+        <v>-3.0815</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.81</v>
+        <v>-3.6023</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3338</v>
+        <v>0.5208</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4787</v>
+        <v>-1.4559</v>
       </c>
       <c r="H11" t="n">
-        <v>-2.9231</v>
+        <v>-1.4994</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5556</v>
+        <v>0.0436</v>
       </c>
       <c r="J11" t="n">
-        <v>-2.2775</v>
+        <v>-0.5049</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.0397</v>
+        <v>-0.7625999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.2378</v>
+        <v>0.2576</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2012</v>
+        <v>-0.9509</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8834</v>
+        <v>-0.7369</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.3178</v>
+        <v>-0.214</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.232</v>
+        <v>-2.7834</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3917</v>
+        <v>-3.7112</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1598</v>
+        <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0307</v>
+        <v>1.1578</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0395</v>
+        <v>0.472</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.008800000000000001</v>
+        <v>0.6858</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>0.8197</v>
+        <v>0.1418</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2836</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.2344</v>
+        <v>-3.563</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.4241</v>
+        <v>-1.3494</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8103</v>
+        <v>-2.2136</v>
       </c>
       <c r="G12" t="n">
         <v>-4.0295</v>
@@ -1390,13 +1390,13 @@
         <v>1.8556</v>
       </c>
       <c r="S12" t="n">
-        <v>0.5605</v>
+        <v>0.232</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4832</v>
+        <v>-0.4086</v>
       </c>
       <c r="U12" t="n">
-        <v>1.0438</v>
+        <v>0.6405</v>
       </c>
       <c r="V12" t="n">
         <v>0.9304</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.5418</v>
+        <v>-5.8472</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.771</v>
+        <v>-2.9755</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.7708</v>
+        <v>-2.8717</v>
       </c>
       <c r="G13" t="n">
         <v>-0.8665</v>
@@ -1468,13 +1468,13 @@
         <v>1.1598</v>
       </c>
       <c r="S13" t="n">
-        <v>0.554</v>
+        <v>0.2486</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1142</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>0.4397</v>
+        <v>0.3389</v>
       </c>
       <c r="V13" t="n">
         <v>-1.7501</v>
@@ -1501,25 +1501,25 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-26.0856</v>
+        <v>-25.3388</v>
       </c>
       <c r="E14" t="n">
-        <v>-16.2364</v>
+        <v>-15.4897</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.8491</v>
+        <v>-9.8492</v>
       </c>
       <c r="G14" t="n">
         <v>-19.8926</v>
       </c>
       <c r="H14" t="n">
-        <v>-9.921099999999999</v>
+        <v>-9.921100000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>-9.971300000000001</v>
+        <v>-9.971299999999999</v>
       </c>
       <c r="J14" t="n">
-        <v>3.751799999999999</v>
+        <v>3.7518</v>
       </c>
       <c r="K14" t="n">
         <v>1.5949</v>
@@ -1546,13 +1546,13 @@
         <v>11.5979</v>
       </c>
       <c r="S14" t="n">
-        <v>2.438</v>
+        <v>3.185</v>
       </c>
       <c r="T14" t="n">
-        <v>-2.2186</v>
+        <v>-1.472</v>
       </c>
       <c r="U14" t="n">
-        <v>4.656600000000001</v>
+        <v>4.6566</v>
       </c>
       <c r="V14" t="n">
         <v>0.6468</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>9.240600000000001</v>
+        <v>8.113200000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>5.8752</v>
+        <v>5.2854</v>
       </c>
       <c r="F15" t="n">
-        <v>3.3655</v>
+        <v>2.8278</v>
       </c>
       <c r="G15" t="n">
         <v>4.8039</v>
@@ -1624,13 +1624,13 @@
         <v>1.8556</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3671</v>
+        <v>0.2396</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8259</v>
+        <v>0.2361</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5412</v>
+        <v>0.0035</v>
       </c>
       <c r="V15" t="n">
         <v>1.214</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.4824</v>
+        <v>4.977</v>
       </c>
       <c r="E16" t="n">
-        <v>3.0753</v>
+        <v>2.6035</v>
       </c>
       <c r="F16" t="n">
-        <v>2.4071</v>
+        <v>2.3735</v>
       </c>
       <c r="G16" t="n">
         <v>3.8277</v>
@@ -1702,13 +1702,13 @@
         <v>2.3195</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1287</v>
+        <v>-0.6341</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.2592</v>
+        <v>-0.731</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1305</v>
+        <v>0.0969</v>
       </c>
       <c r="V16" t="n">
         <v>-0.5361</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>4.0819</v>
+        <v>4.6703</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6007</v>
+        <v>2.7187</v>
       </c>
       <c r="F17" t="n">
-        <v>1.4811</v>
+        <v>1.9516</v>
       </c>
       <c r="G17" t="n">
         <v>5.7527</v>
@@ -1780,13 +1780,13 @@
         <v>2.3195</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6166</v>
+        <v>-1.0282</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.1202</v>
+        <v>-1.0023</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.4964</v>
+        <v>-0.0259</v>
       </c>
       <c r="V17" t="n">
         <v>-1.214</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>3.3136</v>
+        <v>3.1791</v>
       </c>
       <c r="E18" t="n">
         <v>1.765</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5485</v>
+        <v>1.4141</v>
       </c>
       <c r="G18" t="n">
         <v>1.0169</v>
@@ -1858,13 +1858,13 @@
         <v>2.3195</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0228</v>
+        <v>-0.1573</v>
       </c>
       <c r="T18" t="n">
         <v>-0.9709</v>
       </c>
       <c r="U18" t="n">
-        <v>0.948</v>
+        <v>0.8136</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>2.1015</v>
+        <v>1.95</v>
       </c>
       <c r="E19" t="n">
-        <v>1.5547</v>
+        <v>1.4367</v>
       </c>
       <c r="F19" t="n">
-        <v>0.5469000000000001</v>
+        <v>0.5133</v>
       </c>
       <c r="G19" t="n">
         <v>1.1962</v>
@@ -1936,13 +1936,13 @@
         <v>1.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6734</v>
+        <v>0.5219</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1889</v>
+        <v>0.0709</v>
       </c>
       <c r="U19" t="n">
-        <v>0.4846</v>
+        <v>0.4509</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>T. WARD</t>
+          <t>T. WALKUP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,64 +1969,64 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.4074</v>
+        <v>1.7077</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5959</v>
+        <v>-0.367</v>
       </c>
       <c r="F20" t="n">
-        <v>3.0033</v>
+        <v>2.0747</v>
       </c>
       <c r="G20" t="n">
-        <v>0.8862</v>
+        <v>3.1486</v>
       </c>
       <c r="H20" t="n">
-        <v>0.6519</v>
+        <v>2.4225</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2343</v>
+        <v>0.7262</v>
       </c>
       <c r="J20" t="n">
-        <v>0.4752</v>
+        <v>4.2206</v>
       </c>
       <c r="K20" t="n">
-        <v>0.7597</v>
+        <v>2.541</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2845</v>
+        <v>1.6796</v>
       </c>
       <c r="M20" t="n">
-        <v>0.411</v>
+        <v>-1.072</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.1078</v>
+        <v>-0.1186</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5188</v>
+        <v>-0.9534</v>
       </c>
       <c r="P20" t="n">
-        <v>1.3917</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.1598</v>
+        <v>-3.4793</v>
       </c>
       <c r="R20" t="n">
-        <v>2.5515</v>
+        <v>2.7834</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.154</v>
+        <v>-0.7451</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.1949</v>
+        <v>-1.1084</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0409</v>
+        <v>0.3633</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>T. WALKUP</t>
+          <t>T. WARD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,64 +2047,64 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.4046</v>
+        <v>1.3573</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6029</v>
+        <v>-1.4779</v>
       </c>
       <c r="F21" t="n">
-        <v>2.0075</v>
+        <v>2.8353</v>
       </c>
       <c r="G21" t="n">
-        <v>3.1486</v>
+        <v>0.8862</v>
       </c>
       <c r="H21" t="n">
-        <v>2.4225</v>
+        <v>0.6519</v>
       </c>
       <c r="I21" t="n">
-        <v>0.7262</v>
+        <v>0.2343</v>
       </c>
       <c r="J21" t="n">
-        <v>4.2206</v>
+        <v>0.4752</v>
       </c>
       <c r="K21" t="n">
-        <v>2.541</v>
+        <v>0.7597</v>
       </c>
       <c r="L21" t="n">
-        <v>1.6796</v>
+        <v>-0.2845</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.072</v>
+        <v>0.411</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.1186</v>
+        <v>-0.1078</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.9534</v>
+        <v>0.5188</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.6959</v>
+        <v>1.3917</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.4793</v>
+        <v>-1.1598</v>
       </c>
       <c r="R21" t="n">
-        <v>2.7834</v>
+        <v>2.5515</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0482</v>
+        <v>-1.2041</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3443</v>
+        <v>-1.0769</v>
       </c>
       <c r="U21" t="n">
-        <v>0.2961</v>
+        <v>-0.1272</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.2836</v>
       </c>
       <c r="X21" t="n">
         <v>0</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.07820000000000001</v>
+        <v>0.4437</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.5356</v>
+        <v>-0.1817</v>
       </c>
       <c r="F22" t="n">
-        <v>0.4574</v>
+        <v>0.6254</v>
       </c>
       <c r="G22" t="n">
         <v>0.8098</v>
@@ -2170,13 +2170,13 @@
         <v>1.3917</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.5838</v>
+        <v>-0.0619</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>0.0551</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2851</v>
+        <v>-0.1171</v>
       </c>
       <c r="V22" t="n">
         <v>-0.5361</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3827</v>
+        <v>0.0891</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.6741</v>
+        <v>-1.2023</v>
       </c>
       <c r="F23" t="n">
         <v>1.2914</v>
@@ -2248,10 +2248,10 @@
         <v>2.0876</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.0905</v>
+        <v>0.3813</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5975</v>
+        <v>-0.1256</v>
       </c>
       <c r="U23" t="n">
         <v>0.507</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4856</v>
+        <v>-0.4019</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.6133999999999999</v>
+        <v>-0.7314000000000001</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1278</v>
+        <v>0.3295</v>
       </c>
       <c r="G24" t="n">
         <v>-1.4893</v>
@@ -2326,13 +2326,13 @@
         <v>1.8556</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1661</v>
+        <v>0.2497</v>
       </c>
       <c r="T24" t="n">
-        <v>0.1142</v>
+        <v>-0.0037</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0518</v>
+        <v>0.2535</v>
       </c>
       <c r="V24" t="n">
         <v>0.1418</v>
@@ -2365,7 +2365,7 @@
         <v>9.848999999999998</v>
       </c>
       <c r="F25" t="n">
-        <v>16.2365</v>
+        <v>16.2366</v>
       </c>
       <c r="G25" t="n">
         <v>19.8925</v>
@@ -2377,7 +2377,7 @@
         <v>9.9712</v>
       </c>
       <c r="J25" t="n">
-        <v>23.6441</v>
+        <v>23.64409999999999</v>
       </c>
       <c r="K25" t="n">
         <v>11.5161</v>
@@ -2404,13 +2404,13 @@
         <v>20.8756</v>
       </c>
       <c r="S25" t="n">
-        <v>-2.438</v>
+        <v>-2.4382</v>
       </c>
       <c r="T25" t="n">
-        <v>-4.6567</v>
+        <v>-4.656700000000001</v>
       </c>
       <c r="U25" t="n">
-        <v>2.2186</v>
+        <v>2.2185</v>
       </c>
       <c r="V25" t="n">
         <v>-0.6467999999999999</v>
